--- a/user_inputs/terms_missing_only.xlsx
+++ b/user_inputs/terms_missing_only.xlsx
@@ -341,7 +341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="3">
@@ -513,7 +513,74 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="49.25" customHeight="1" s="3"/>
+    <row r="3" ht="49.25" customHeight="1" s="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LVDT-2 Pre-Trim</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LVDT-2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pre-Trim</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sine Sweep</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="49.25" customHeight="1" s="3"/>
     <row r="5" ht="49.25" customHeight="1" s="3"/>
     <row r="6" ht="49.25" customHeight="1" s="3"/>
